--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24332,7 +24332,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -30126,7 +30126,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30818,7 +30818,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31214,7 +31214,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34378,16 +34378,16 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O203" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q203" t="n">
         <v>0</v>
       </c>
       <c r="R203" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36846,7 +36846,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36998,16 +36998,16 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O218" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>0.208593237428971</v>
+        <v>0.2129389298754079</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -37160,10 +37160,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O219" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -37394,16 +37394,16 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O220" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q220" t="n">
         <v>0</v>
       </c>
       <c r="R220" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -38726,16 +38726,16 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O229" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>0.08691384892873792</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -40110,16 +40110,16 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O237" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q237" t="n">
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2390130845540293</v>
+        <v>0.2433587770004662</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41542,16 +41542,16 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O246" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="Q246" t="n">
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0.9517066457696802</v>
+        <v>0.9603980306625541</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42478,7 +42478,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42630,16 +42630,16 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O252" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="Q252" t="n">
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.07822246403586412</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -42792,10 +42792,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O253" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -42874,7 +42874,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -43026,16 +43026,16 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O254" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q254" t="n">
         <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -43188,10 +43188,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O255" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -43422,16 +43422,16 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="O256" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Q256" t="n">
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.03476553957149517</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -43570,16 +43570,16 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="O257" t="n">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="Q257" t="n">
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0.4476063219830003</v>
+        <v>0.5736314029296703</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43718,16 +43718,16 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="O258" t="n">
-        <v>179</v>
+        <v>213</v>
       </c>
       <c r="Q258" t="n">
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0.7778789479122045</v>
+        <v>0.9256324910910589</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44806,16 +44806,16 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O264" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.04780261691080586</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -45198,7 +45198,7 @@
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
@@ -45469,17 +45469,17 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>D172</t>
+          <t>D170</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Severe complicated influenza</t>
+          <t>Complicated varicella</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>流感并发重症</t>
+          <t>水痘并发症</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
@@ -45498,16 +45498,16 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="O268" t="n">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.1607906205181651</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -45617,17 +45617,17 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>D181</t>
+          <t>D172</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Severe complicated COVID-19</t>
+          <t>Severe complicated influenza</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>新冠并发重症</t>
+          <t>流感并发重症</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -45662,42 +45662,28 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR269" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -45764,7 +45750,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -45808,103 +45794,31 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O270" t="n">
-        <v>50</v>
+        <v>55</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0.2390130845540293</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U270" t="inlineStr">
         <is>
           <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>新冠併發重症</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA270" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
@@ -45998,7 +45912,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -46013,17 +45927,17 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>D210</t>
+          <t>D181</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Acute hepatitis C</t>
+          <t>Severe complicated COVID-19</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>急性丙型肝炎</t>
+          <t>新冠并发重症</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -46042,25 +45956,39 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>6</v>
+        <v>55</v>
       </c>
       <c r="O271" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0.02607415467862137</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>55</v>
       </c>
       <c r="U271" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA271" t="inlineStr">
@@ -46068,6 +45996,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.8</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46085,7 +46071,7 @@
       </c>
       <c r="AS271" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AT271" t="n">
@@ -46160,7 +46146,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -46204,103 +46190,31 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O272" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.03041984712505827</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U272" t="inlineStr">
         <is>
           <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
         </is>
       </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>急性病毒性Ｃ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA272" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Acute hepatitis C, code 0705.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
@@ -46366,6 +46280,240 @@
         </is>
       </c>
       <c r="BC272" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N273" t="n">
+        <v>7</v>
+      </c>
+      <c r="O273" t="n">
+        <v>7</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｃ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.8</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C, code 0705.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO273" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP273" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AT273" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU273" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV273" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ273" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA273" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB273" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC273" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -46487,7 +46635,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
@@ -46497,7 +46645,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -46549,7 +46697,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7798</v>
+        <v>7897</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1004,7 +1004,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6354,7 +6354,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6750,7 +6750,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7146,7 +7146,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12644,7 +12644,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14520,7 +14520,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14916,7 +14916,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16658,7 +16658,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17942,7 +17942,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18338,7 +18338,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22404,7 +22404,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23540,7 +23540,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23936,7 +23936,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24332,7 +24332,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26308,7 +26308,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26704,7 +26704,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29730,7 +29730,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -30126,7 +30126,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30818,7 +30818,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31214,7 +31214,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -33090,7 +33090,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34770,7 +34770,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -36054,7 +36054,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36450,7 +36450,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36846,7 +36846,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -37242,7 +37242,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -37690,16 +37690,16 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O222" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Q222" t="n">
         <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>0.1434078507324176</v>
+        <v>0.1477535431788545</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -39022,16 +39022,16 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O231" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q231" t="n">
         <v>0</v>
       </c>
       <c r="R231" t="n">
-        <v>0.02607415467862137</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
@@ -39184,10 +39184,10 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O232" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U232" t="inlineStr">
         <is>
@@ -39266,7 +39266,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -39566,16 +39566,16 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O234" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="Q234" t="n">
         <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>0.07822246403586412</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -39728,10 +39728,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="O235" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -40110,16 +40110,16 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O237" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q237" t="n">
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2433587770004662</v>
+        <v>0.2477044694469031</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41098,16 +41098,16 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="O243" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="Q243" t="n">
         <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>0.1303707733931069</v>
+        <v>0.1347164658395438</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -41542,16 +41542,16 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="O246" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q246" t="n">
         <v>0</v>
       </c>
       <c r="R246" t="n">
-        <v>0.9603980306625541</v>
+        <v>0.964743723108991</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -42082,7 +42082,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42478,7 +42478,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42874,7 +42874,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -43270,7 +43270,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -43570,16 +43570,16 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="O257" t="n">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="Q257" t="n">
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0.5736314029296703</v>
+        <v>0.6344710971797868</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43718,16 +43718,16 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="O258" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="Q258" t="n">
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0.9256324910910589</v>
+        <v>1.042966187144855</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -44258,7 +44258,7 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
@@ -44777,17 +44777,17 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -44806,16 +44806,16 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O264" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
-        <v>0.04780261691080586</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S264" t="inlineStr">
         <is>
@@ -44925,22 +44925,22 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -44954,58 +44954,44 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="O265" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.06083969425011655</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO265" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP265" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR265" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr"/>
       <c r="AT265" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -45072,7 +45058,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -45121,98 +45107,26 @@
       <c r="O266" t="n">
         <v>19</v>
       </c>
+      <c r="Q266" t="n">
+        <v>0</v>
+      </c>
+      <c r="R266" t="n">
+        <v>0.08256815648230102</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U266" t="inlineStr">
         <is>
           <t>SER_TW_HIV_044</t>
         </is>
       </c>
-      <c r="V266" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="W266" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X266" t="inlineStr">
-        <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
-        </is>
-      </c>
-      <c r="Y266" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z266" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA266" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB266" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC266" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD266" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE266" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF266" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG266" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH266" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI266" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ266" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
-        </is>
-      </c>
-      <c r="AK266" t="inlineStr">
-        <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
-        </is>
-      </c>
-      <c r="AM266" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN266" t="b">
-        <v>1</v>
       </c>
       <c r="AO266" t="inlineStr">
         <is>
@@ -45306,7 +45220,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -45321,22 +45235,22 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>D165</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>阿米巴病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -45350,44 +45264,130 @@
         </is>
       </c>
       <c r="N267" t="n">
+        <v>19</v>
+      </c>
+      <c r="O267" t="n">
+        <v>19</v>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI267" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ267" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK267" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM267" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN267" t="b">
         <v>1</v>
       </c>
-      <c r="O267" t="n">
+      <c r="AO267" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP267" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ267" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT267" t="n">
         <v>1</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
-      <c r="R267" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S267" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO267" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP267" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR267" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr"/>
-      <c r="AT267" t="n">
-        <v>0</v>
-      </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
@@ -45469,22 +45469,22 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>D170</t>
+          <t>D165</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Complicated varicella</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>水痘并发症</t>
+          <t>阿米巴病</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -45498,16 +45498,16 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O268" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -45617,17 +45617,17 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>D172</t>
+          <t>D170</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Severe complicated influenza</t>
+          <t>Complicated varicella</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>流感并发重症</t>
+          <t>水痘并发症</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -45646,16 +45646,16 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="O269" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0.2172846223218448</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -45765,17 +45765,17 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>D181</t>
+          <t>D172</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Severe complicated COVID-19</t>
+          <t>Severe complicated influenza</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>新冠并发重症</t>
+          <t>流感并发重症</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
@@ -45794,58 +45794,44 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O270" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>0.2390130845540293</v>
+        <v>0.2477044694469031</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="AA270" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ270" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR270" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr"/>
       <c r="AT270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -45912,7 +45898,7 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -45956,103 +45942,31 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="O271" t="n">
-        <v>55</v>
+        <v>91</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>0.3954580126257575</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U271" t="inlineStr">
         <is>
           <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
-      <c r="V271" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="W271" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X271" t="inlineStr">
-        <is>
-          <t>新冠併發重症</t>
-        </is>
-      </c>
-      <c r="Y271" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z271" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA271" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB271" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC271" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD271" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE271" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF271" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG271" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH271" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI271" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ271" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
-        </is>
-      </c>
-      <c r="AK271" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
-        </is>
-      </c>
-      <c r="AM271" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN271" t="b">
-        <v>1</v>
       </c>
       <c r="AO271" t="inlineStr">
         <is>
@@ -46146,7 +46060,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -46161,17 +46075,17 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>D210</t>
+          <t>D181</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Acute hepatitis C</t>
+          <t>Severe complicated COVID-19</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>急性丙型肝炎</t>
+          <t>新冠并发重症</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -46190,25 +46104,39 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="O272" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0.03041984712505827</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>91</v>
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -46216,6 +46144,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46233,7 +46219,7 @@
       </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -46308,7 +46294,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -46352,103 +46338,31 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O273" t="n">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>0</v>
+      </c>
+      <c r="R273" t="n">
+        <v>0.03911123201793206</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U273" t="inlineStr">
         <is>
           <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
         </is>
       </c>
-      <c r="V273" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
-        </is>
-      </c>
-      <c r="W273" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X273" t="inlineStr">
-        <is>
-          <t>急性病毒性Ｃ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y273" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z273" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA273" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB273" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC273" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD273" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE273" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF273" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG273" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH273" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI273" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ273" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
-        </is>
-      </c>
-      <c r="AK273" t="inlineStr">
-        <is>
-          <t>Acute hepatitis C, code 0705.</t>
-        </is>
-      </c>
-      <c r="AM273" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN273" t="b">
-        <v>1</v>
       </c>
       <c r="AO273" t="inlineStr">
         <is>
@@ -46514,6 +46428,240 @@
         </is>
       </c>
       <c r="BC273" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N274" t="n">
+        <v>9</v>
+      </c>
+      <c r="O274" t="n">
+        <v>9</v>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X274" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｃ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB274" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC274" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD274" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE274" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF274" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG274" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH274" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI274" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ274" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK274" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C, code 0705.</t>
+        </is>
+      </c>
+      <c r="AM274" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN274" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO274" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP274" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AT274" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU274" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV274" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ274" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA274" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB274" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC274" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -46635,7 +46783,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10">
@@ -46645,7 +46793,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11">
@@ -46697,7 +46845,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7897</v>
+        <v>7996</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -36998,16 +36998,16 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O218" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="Q218" t="n">
         <v>0</v>
       </c>
       <c r="R218" t="n">
-        <v>0.2129389298754079</v>
+        <v>0.208593237428971</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -37160,10 +37160,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="O219" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -37986,16 +37986,16 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="O224" t="n">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="Q224" t="n">
         <v>0</v>
       </c>
       <c r="R224" t="n">
-        <v>4.397840755794139</v>
+        <v>4.389149370901265</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -38726,16 +38726,16 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O229" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q229" t="n">
         <v>0</v>
       </c>
       <c r="R229" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.09560523382161172</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -40110,16 +40110,16 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="O237" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q237" t="n">
         <v>0</v>
       </c>
       <c r="R237" t="n">
-        <v>0.2477044694469031</v>
+        <v>0.25205016189334</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -40258,16 +40258,16 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O238" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Q238" t="n">
         <v>0</v>
       </c>
       <c r="R238" t="n">
-        <v>0.06953107914299034</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -42234,16 +42234,16 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O250" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Q250" t="n">
         <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0.1999018525360972</v>
+        <v>0.2042475449825341</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -42396,10 +42396,10 @@
         </is>
       </c>
       <c r="N251" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="O251" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="U251" t="inlineStr">
         <is>
@@ -42630,16 +42630,16 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O252" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q252" t="n">
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.09560523382161172</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -42792,10 +42792,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O253" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -43026,16 +43026,16 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O254" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q254" t="n">
         <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0.02172846223218448</v>
+        <v>0.03041984712505827</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -43188,10 +43188,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O255" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -43422,16 +43422,16 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O256" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Q256" t="n">
         <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.03476553957149517</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -43570,16 +43570,16 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="O257" t="n">
-        <v>146</v>
+        <v>170</v>
       </c>
       <c r="Q257" t="n">
         <v>0</v>
       </c>
       <c r="R257" t="n">
-        <v>0.6344710971797868</v>
+        <v>0.7387677158942723</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43718,16 +43718,16 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="O258" t="n">
-        <v>240</v>
+        <v>292</v>
       </c>
       <c r="Q258" t="n">
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>1.042966187144855</v>
+        <v>1.268942194359574</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -43837,17 +43837,17 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>D058</t>
+          <t>D035</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>Leptospirosis</t>
         </is>
       </c>
       <c r="J259" t="inlineStr">
         <is>
-          <t>恙虫病</t>
+          <t>钩端螺旋体病</t>
         </is>
       </c>
       <c r="K259" t="inlineStr">
@@ -43866,16 +43866,16 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q259" t="n">
         <v>0</v>
       </c>
       <c r="R259" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S259" t="inlineStr">
         <is>
@@ -43985,22 +43985,22 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>D068</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Acute hepatitis B</t>
+          <t>Scrub Typhus</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>急性乙型肝炎</t>
+          <t>恙虫病</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -44014,58 +44014,44 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q260" t="n">
         <v>0</v>
       </c>
       <c r="R260" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
-        </is>
-      </c>
-      <c r="AA260" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ260" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS260" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR260" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS260" t="inlineStr"/>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
@@ -44132,7 +44118,7 @@
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -44181,98 +44167,26 @@
       <c r="O261" t="n">
         <v>1</v>
       </c>
+      <c r="Q261" t="n">
+        <v>0</v>
+      </c>
+      <c r="R261" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U261" t="inlineStr">
         <is>
           <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
-      <c r="V261" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
-        </is>
-      </c>
-      <c r="W261" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X261" t="inlineStr">
-        <is>
-          <t>急性病毒性Ｂ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y261" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z261" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA261" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB261" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC261" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD261" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE261" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF261" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG261" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH261" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI261" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ261" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK261" t="inlineStr">
-        <is>
-          <t>Acute hepatitis B, code 0703.</t>
-        </is>
-      </c>
-      <c r="AM261" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN261" t="b">
-        <v>1</v>
       </c>
       <c r="AO261" t="inlineStr">
         <is>
@@ -44366,7 +44280,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -44381,22 +44295,22 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D068</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Acute hepatitis B</t>
         </is>
       </c>
       <c r="J262" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>急性乙型肝炎</t>
         </is>
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -44415,20 +44329,34 @@
       <c r="O262" t="n">
         <v>1</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
-      <c r="R262" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S262" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U262" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｂ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA262" t="inlineStr">
@@ -44436,9 +44364,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI262" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ262" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK262" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B, code 0703.</t>
+        </is>
+      </c>
+      <c r="AM262" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN262" t="b">
+        <v>1</v>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
@@ -44448,12 +44434,12 @@
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT262" t="n">
@@ -44461,7 +44447,7 @@
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
@@ -44528,7 +44514,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -44572,103 +44558,31 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O263" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" t="n">
+        <v>0.008691384892873792</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U263" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V263" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W263" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X263" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y263" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z263" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA263" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB263" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC263" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD263" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE263" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF263" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG263" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH263" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI263" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ263" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK263" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM263" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN263" t="b">
-        <v>1</v>
       </c>
       <c r="AO263" t="inlineStr">
         <is>
@@ -44762,7 +44676,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -44777,17 +44691,17 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J264" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K264" t="inlineStr">
@@ -44806,44 +44720,130 @@
         </is>
       </c>
       <c r="N264" t="n">
+        <v>2</v>
+      </c>
+      <c r="O264" t="n">
+        <v>2</v>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI264" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ264" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK264" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM264" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN264" t="b">
         <v>1</v>
       </c>
-      <c r="O264" t="n">
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AT264" t="n">
         <v>1</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO264" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP264" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR264" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr"/>
-      <c r="AT264" t="n">
-        <v>0</v>
-      </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
@@ -44925,17 +44925,17 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -44954,16 +44954,16 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O265" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="Q265" t="n">
         <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>0.06083969425011655</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -45073,22 +45073,22 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -45102,58 +45102,44 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O266" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="Q266" t="n">
         <v>0</v>
       </c>
       <c r="R266" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR266" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
@@ -45220,7 +45206,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -45235,22 +45221,22 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -45264,130 +45250,44 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="O267" t="n">
-        <v>19</v>
-      </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN267" t="b">
         <v>1</v>
       </c>
+      <c r="Q267" t="n">
+        <v>0</v>
+      </c>
+      <c r="R267" t="n">
+        <v>0.004345692446436896</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR267" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
@@ -45469,22 +45369,22 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>D165</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>阿米巴病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -45498,44 +45398,58 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="O268" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="Q268" t="n">
         <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.09125954137517482</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR268" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
@@ -45602,7 +45516,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -45617,17 +45531,17 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>D170</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>Complicated varicella</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>水痘并发症</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K269" t="inlineStr">
@@ -45646,44 +45560,130 @@
         </is>
       </c>
       <c r="N269" t="n">
+        <v>21</v>
+      </c>
+      <c r="O269" t="n">
+        <v>21</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
         <v>1</v>
       </c>
-      <c r="O269" t="n">
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="AT269" t="n">
         <v>1</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO269" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP269" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR269" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
-      <c r="AT269" t="n">
-        <v>0</v>
-      </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
@@ -45765,22 +45765,22 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>D172</t>
+          <t>D165</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Severe complicated influenza</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>流感并发重症</t>
+          <t>阿米巴病</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -45794,16 +45794,16 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="O270" t="n">
-        <v>57</v>
+        <v>4</v>
       </c>
       <c r="Q270" t="n">
         <v>0</v>
       </c>
       <c r="R270" t="n">
-        <v>0.2477044694469031</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -45913,17 +45913,17 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>D181</t>
+          <t>D170</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Severe complicated COVID-19</t>
+          <t>Complicated varicella</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>新冠并发重症</t>
+          <t>水痘并发症</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
@@ -45942,58 +45942,44 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="O271" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="Q271" t="n">
         <v>0</v>
       </c>
       <c r="R271" t="n">
-        <v>0.3954580126257575</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ271" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR271" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr"/>
       <c r="AT271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
@@ -46060,7 +46046,7 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -46075,17 +46061,17 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>D181</t>
+          <t>D172</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Severe complicated COVID-19</t>
+          <t>Severe complicated influenza</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>新冠并发重症</t>
+          <t>流感并发重症</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -46104,130 +46090,44 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="O272" t="n">
-        <v>91</v>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>新冠併發重症</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA272" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
+        <v>83</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>0</v>
+      </c>
+      <c r="R272" t="n">
+        <v>0.3606924730542624</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ272" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR272" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr"/>
       <c r="AT272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
@@ -46309,17 +46209,17 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>D210</t>
+          <t>D181</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Acute hepatitis C</t>
+          <t>Severe complicated COVID-19</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>急性丙型肝炎</t>
+          <t>新冠并发重症</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
@@ -46338,16 +46238,16 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="O273" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="Q273" t="n">
         <v>0</v>
       </c>
       <c r="R273" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.4519520144294372</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -46356,7 +46256,7 @@
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AA273" t="inlineStr">
@@ -46381,7 +46281,7 @@
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -46471,17 +46371,17 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>D210</t>
+          <t>D181</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Acute hepatitis C</t>
+          <t>Severe complicated COVID-19</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>急性丙型肝炎</t>
+          <t>新冠并发重症</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
@@ -46500,19 +46400,19 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="O274" t="n">
-        <v>9</v>
+        <v>104</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="V274" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="W274" t="inlineStr">
@@ -46522,7 +46422,7 @@
       </c>
       <c r="X274" t="inlineStr">
         <is>
-          <t>急性病毒性Ｃ型肝炎</t>
+          <t>新冠併發重症</t>
         </is>
       </c>
       <c r="Y274" t="inlineStr">
@@ -46587,7 +46487,7 @@
       </c>
       <c r="AK274" t="inlineStr">
         <is>
-          <t>Acute hepatitis C, code 0705.</t>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
         </is>
       </c>
       <c r="AM274" t="inlineStr">
@@ -46615,7 +46515,7 @@
       </c>
       <c r="AS274" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AT274" t="n">
@@ -46662,6 +46562,402 @@
         </is>
       </c>
       <c r="BC274" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N275" t="n">
+        <v>14</v>
+      </c>
+      <c r="O275" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>0</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0.06083969425011655</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO275" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP275" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AT275" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU275" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV275" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ275" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA275" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB275" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC275" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N276" t="n">
+        <v>14</v>
+      </c>
+      <c r="O276" t="n">
+        <v>14</v>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｃ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C, code 0705.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO276" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP276" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AT276" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU276" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV276" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ276" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA276" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB276" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC276" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -46783,7 +47079,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -46793,7 +47089,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
@@ -46845,7 +47141,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7996</v>
+        <v>8128</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>59</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0.2563958543397769</v>
       </c>
@@ -1014,7 +1011,7 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN3" t="b">
@@ -1410,7 +1407,7 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN5" t="b">
@@ -2990,7 +2987,7 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN15" t="b">
@@ -4583,9 +4580,6 @@
       <c r="O25" t="n">
         <v>98</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.4258778597508158</v>
       </c>
@@ -4832,7 +4826,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -5968,7 +5962,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6364,7 +6358,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN35" t="b">
@@ -6511,9 +6505,6 @@
       <c r="O36" t="n">
         <v>42</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.1825190827503496</v>
       </c>
@@ -6760,7 +6751,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7156,7 +7147,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN39" t="b">
@@ -8588,7 +8579,7 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN48" t="b">
@@ -10081,9 +10072,6 @@
       <c r="O58" t="n">
         <v>83</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.3606924730542624</v>
       </c>
@@ -10330,7 +10318,7 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN59" t="b">
@@ -11466,7 +11454,7 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN66" t="b">
@@ -11862,7 +11850,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -12009,9 +11997,6 @@
       <c r="O69" t="n">
         <v>50</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.2172846223218448</v>
       </c>
@@ -12258,7 +12243,7 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN70" t="b">
@@ -12654,7 +12639,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -14530,7 +14515,7 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN84" t="b">
@@ -16419,9 +16404,6 @@
       <c r="O96" t="n">
         <v>106</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0.460643399322311</v>
       </c>
@@ -16668,7 +16650,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -17952,7 +17934,7 @@
       </c>
       <c r="AM105" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN105" t="b">
@@ -18348,7 +18330,7 @@
       </c>
       <c r="AM107" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN107" t="b">
@@ -18495,9 +18477,6 @@
       <c r="O108" t="n">
         <v>42</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.1825190827503496</v>
       </c>
@@ -18744,7 +18723,7 @@
       </c>
       <c r="AM109" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN109" t="b">
@@ -18891,9 +18870,6 @@
       <c r="O110" t="n">
         <v>86</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.373729550393573</v>
       </c>
@@ -19140,7 +19116,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -19287,9 +19263,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -19435,9 +19408,6 @@
       <c r="O113" t="n">
         <v>5</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -19583,9 +19553,6 @@
       <c r="O114" t="n">
         <v>21</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.09125954137517482</v>
       </c>
@@ -19731,9 +19698,6 @@
       <c r="O115" t="n">
         <v>2</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -19879,9 +19843,6 @@
       <c r="O116" t="n">
         <v>3</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -20027,9 +19988,6 @@
       <c r="O117" t="n">
         <v>1</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -20175,9 +20133,6 @@
       <c r="O118" t="n">
         <v>15</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.06518538669655344</v>
       </c>
@@ -20323,9 +20278,6 @@
       <c r="O119" t="n">
         <v>2</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -20471,9 +20423,6 @@
       <c r="O120" t="n">
         <v>15</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.06518538669655344</v>
       </c>
@@ -20720,7 +20669,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -20867,9 +20816,6 @@
       <c r="O122" t="n">
         <v>1</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -21263,9 +21209,6 @@
       <c r="O124" t="n">
         <v>10</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.04345692446436896</v>
       </c>
@@ -21425,9 +21368,6 @@
       <c r="O125" t="n">
         <v>22</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0.09560523382161172</v>
       </c>
@@ -21573,9 +21513,6 @@
       <c r="O126" t="n">
         <v>66</v>
       </c>
-      <c r="Q126" t="n">
-        <v>0</v>
-      </c>
       <c r="R126" t="n">
         <v>0.2868157014648351</v>
       </c>
@@ -21721,9 +21658,6 @@
       <c r="O127" t="n">
         <v>16</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.06953107914299034</v>
       </c>
@@ -21869,9 +21803,6 @@
       <c r="O128" t="n">
         <v>3</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -22017,9 +21948,6 @@
       <c r="O129" t="n">
         <v>2</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -22165,9 +22093,6 @@
       <c r="O130" t="n">
         <v>82</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.3563467806078255</v>
       </c>
@@ -22414,7 +22339,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -22561,9 +22486,6 @@
       <c r="O132" t="n">
         <v>28</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.1216793885002331</v>
       </c>
@@ -22709,9 +22631,6 @@
       <c r="O133" t="n">
         <v>1</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -22857,9 +22776,6 @@
       <c r="O134" t="n">
         <v>3</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -23005,9 +22921,6 @@
       <c r="O135" t="n">
         <v>38</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.165136312964602</v>
       </c>
@@ -23153,9 +23066,6 @@
       <c r="O136" t="n">
         <v>5</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -23301,9 +23211,6 @@
       <c r="O137" t="n">
         <v>3</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -23550,7 +23457,7 @@
       </c>
       <c r="AM138" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN138" t="b">
@@ -23697,9 +23604,6 @@
       <c r="O139" t="n">
         <v>47</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.2042475449825341</v>
       </c>
@@ -23946,7 +23850,7 @@
       </c>
       <c r="AM140" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN140" t="b">
@@ -24093,9 +23997,6 @@
       <c r="O141" t="n">
         <v>56</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.2433587770004662</v>
       </c>
@@ -24342,7 +24243,7 @@
       </c>
       <c r="AM142" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN142" t="b">
@@ -24489,9 +24390,6 @@
       <c r="O143" t="n">
         <v>77</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0.334618318375641</v>
       </c>
@@ -24738,7 +24636,7 @@
       </c>
       <c r="AM144" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN144" t="b">
@@ -24885,9 +24783,6 @@
       <c r="O145" t="n">
         <v>2</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -25033,9 +24928,6 @@
       <c r="O146" t="n">
         <v>1</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -25181,9 +25073,6 @@
       <c r="O147" t="n">
         <v>16</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.06953107914299034</v>
       </c>
@@ -25329,9 +25218,6 @@
       <c r="O148" t="n">
         <v>5</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -25477,9 +25363,6 @@
       <c r="O149" t="n">
         <v>1</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -25625,9 +25508,6 @@
       <c r="O150" t="n">
         <v>1</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -25773,9 +25653,6 @@
       <c r="O151" t="n">
         <v>43</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.1868647751967865</v>
       </c>
@@ -25921,9 +25798,6 @@
       <c r="O152" t="n">
         <v>6</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.02607415467862137</v>
       </c>
@@ -26069,9 +25943,6 @@
       <c r="O153" t="n">
         <v>17</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.07387677158942724</v>
       </c>
@@ -26318,7 +26189,7 @@
       </c>
       <c r="AM154" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN154" t="b">
@@ -26465,9 +26336,6 @@
       <c r="O155" t="n">
         <v>1</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -26861,9 +26729,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -27009,9 +26874,6 @@
       <c r="O158" t="n">
         <v>14</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.06083969425011655</v>
       </c>
@@ -27171,9 +27033,6 @@
       <c r="O159" t="n">
         <v>31</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.1347164658395438</v>
       </c>
@@ -27319,9 +27178,6 @@
       <c r="O160" t="n">
         <v>77</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.334618318375641</v>
       </c>
@@ -27467,9 +27323,6 @@
       <c r="O161" t="n">
         <v>20</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.08691384892873792</v>
       </c>
@@ -27615,9 +27468,6 @@
       <c r="O162" t="n">
         <v>1</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -27763,9 +27613,6 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -27911,9 +27758,6 @@
       <c r="O164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -28059,9 +27903,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -28207,9 +28048,6 @@
       <c r="O166" t="n">
         <v>93</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.4041493975186313</v>
       </c>
@@ -28456,7 +28294,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -28603,9 +28441,6 @@
       <c r="O168" t="n">
         <v>26</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.1129880036073593</v>
       </c>
@@ -28751,9 +28586,6 @@
       <c r="O169" t="n">
         <v>1</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -28899,9 +28731,6 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -29047,9 +28876,6 @@
       <c r="O171" t="n">
         <v>37</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.1607906205181651</v>
       </c>
@@ -29195,9 +29021,6 @@
       <c r="O172" t="n">
         <v>2</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -29343,9 +29166,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -29491,9 +29311,6 @@
       <c r="O174" t="n">
         <v>6</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.02607415467862137</v>
       </c>
@@ -29740,7 +29557,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -29887,9 +29704,6 @@
       <c r="O176" t="n">
         <v>27</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.1173336960537962</v>
       </c>
@@ -30136,7 +29950,7 @@
       </c>
       <c r="AM177" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN177" t="b">
@@ -30283,9 +30097,6 @@
       <c r="O178" t="n">
         <v>1</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -30431,9 +30242,6 @@
       <c r="O179" t="n">
         <v>2</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -30579,9 +30387,6 @@
       <c r="O180" t="n">
         <v>51</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.2216303147682817</v>
       </c>
@@ -30828,7 +30633,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -30975,9 +30780,6 @@
       <c r="O182" t="n">
         <v>58</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.25205016189334</v>
       </c>
@@ -31224,7 +31026,7 @@
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -31371,9 +31173,6 @@
       <c r="O184" t="n">
         <v>4</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -31519,9 +31318,6 @@
       <c r="O185" t="n">
         <v>22</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.09560523382161172</v>
       </c>
@@ -31667,9 +31463,6 @@
       <c r="O186" t="n">
         <v>520</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>2.259760072147186</v>
       </c>
@@ -31815,9 +31608,6 @@
       <c r="O187" t="n">
         <v>987</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>4.289198444633216</v>
       </c>
@@ -31963,9 +31753,6 @@
       <c r="O188" t="n">
         <v>10</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.04345692446436896</v>
       </c>
@@ -32111,9 +31898,6 @@
       <c r="O189" t="n">
         <v>1</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -32259,9 +32043,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -32407,9 +32188,6 @@
       <c r="O191" t="n">
         <v>1</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -32555,9 +32333,6 @@
       <c r="O192" t="n">
         <v>28</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.1216793885002331</v>
       </c>
@@ -32703,9 +32478,6 @@
       <c r="O193" t="n">
         <v>4</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -32851,9 +32623,6 @@
       <c r="O194" t="n">
         <v>7</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -33100,7 +32869,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -33242,16 +33011,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O196" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R196" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -33395,9 +33161,6 @@
       <c r="O197" t="n">
         <v>11</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.04780261691080586</v>
       </c>
@@ -33644,7 +33407,7 @@
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN198" t="b">
@@ -33791,9 +33554,6 @@
       <c r="O199" t="n">
         <v>21</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.09125954137517482</v>
       </c>
@@ -33939,9 +33699,6 @@
       <c r="O200" t="n">
         <v>59</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.2563958543397769</v>
       </c>
@@ -34087,9 +33844,6 @@
       <c r="O201" t="n">
         <v>13</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.05649400180367965</v>
       </c>
@@ -34235,9 +33989,6 @@
       <c r="O202" t="n">
         <v>1</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -34378,16 +34129,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O203" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q203" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R203" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -34531,9 +34279,6 @@
       <c r="O204" t="n">
         <v>100</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.4345692446436896</v>
       </c>
@@ -34780,7 +34525,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -34927,9 +34672,6 @@
       <c r="O206" t="n">
         <v>30</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.1303707733931069</v>
       </c>
@@ -35075,9 +34817,6 @@
       <c r="O207" t="n">
         <v>4</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -35223,9 +34962,6 @@
       <c r="O208" t="n">
         <v>4</v>
       </c>
-      <c r="Q208" t="n">
-        <v>0</v>
-      </c>
       <c r="R208" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -35371,9 +35107,6 @@
       <c r="O209" t="n">
         <v>63</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.2737786241255245</v>
       </c>
@@ -35519,9 +35252,6 @@
       <c r="O210" t="n">
         <v>5</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -35667,9 +35397,6 @@
       <c r="O211" t="n">
         <v>1</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -35815,9 +35542,6 @@
       <c r="O212" t="n">
         <v>38</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.165136312964602</v>
       </c>
@@ -36064,7 +35788,7 @@
       </c>
       <c r="AM213" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN213" t="b">
@@ -36211,9 +35935,6 @@
       <c r="O214" t="n">
         <v>35</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.1520992356252913</v>
       </c>
@@ -36460,7 +36181,7 @@
       </c>
       <c r="AM215" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN215" t="b">
@@ -36607,9 +36328,6 @@
       <c r="O216" t="n">
         <v>56</v>
       </c>
-      <c r="Q216" t="n">
-        <v>0</v>
-      </c>
       <c r="R216" t="n">
         <v>0.2433587770004662</v>
       </c>
@@ -36856,7 +36574,7 @@
       </c>
       <c r="AM217" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN217" t="b">
@@ -36998,16 +36716,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O218" t="n">
-        <v>48</v>
-      </c>
-      <c r="Q218" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="R218" t="n">
-        <v>0.208593237428971</v>
+        <v>0.2129389298754079</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -37160,10 +36875,10 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O219" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U219" t="inlineStr">
         <is>
@@ -37252,7 +36967,7 @@
       </c>
       <c r="AM219" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN219" t="b">
@@ -37399,9 +37114,6 @@
       <c r="O220" t="n">
         <v>4</v>
       </c>
-      <c r="Q220" t="n">
-        <v>0</v>
-      </c>
       <c r="R220" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -37547,9 +37259,6 @@
       <c r="O221" t="n">
         <v>5</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -37695,9 +37404,6 @@
       <c r="O222" t="n">
         <v>34</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.1477535431788545</v>
       </c>
@@ -37843,9 +37549,6 @@
       <c r="O223" t="n">
         <v>508</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>2.207611762789943</v>
       </c>
@@ -37991,9 +37694,6 @@
       <c r="O224" t="n">
         <v>1010</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>4.389149370901265</v>
       </c>
@@ -38139,9 +37839,6 @@
       <c r="O225" t="n">
         <v>2</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.008691384892873792</v>
       </c>
@@ -38287,9 +37984,6 @@
       <c r="O226" t="n">
         <v>1</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -38435,9 +38129,6 @@
       <c r="O227" t="n">
         <v>1</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -38583,9 +38274,6 @@
       <c r="O228" t="n">
         <v>3</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.01303707733931069</v>
       </c>
@@ -38731,9 +38419,6 @@
       <c r="O229" t="n">
         <v>22</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0.09560523382161172</v>
       </c>
@@ -38879,9 +38564,6 @@
       <c r="O230" t="n">
         <v>7</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -39027,9 +38709,6 @@
       <c r="O231" t="n">
         <v>7</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -39276,7 +38955,7 @@
       </c>
       <c r="AM232" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN232" t="b">
@@ -39423,9 +39102,6 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -39571,9 +39247,6 @@
       <c r="O234" t="n">
         <v>20</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.08691384892873792</v>
       </c>
@@ -39820,7 +39493,7 @@
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -39967,9 +39640,6 @@
       <c r="O236" t="n">
         <v>16</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.06953107914299034</v>
       </c>
@@ -40115,9 +39785,6 @@
       <c r="O237" t="n">
         <v>58</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.25205016189334</v>
       </c>
@@ -40263,9 +39930,6 @@
       <c r="O238" t="n">
         <v>19</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.08256815648230102</v>
       </c>
@@ -40411,9 +40075,6 @@
       <c r="O239" t="n">
         <v>5</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.02172846223218448</v>
       </c>
@@ -40559,9 +40220,6 @@
       <c r="O240" t="n">
         <v>1</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -40707,9 +40365,6 @@
       <c r="O241" t="n">
         <v>89</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.3867666277328837</v>
       </c>
@@ -40956,7 +40611,7 @@
       </c>
       <c r="AM242" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN242" t="b">
@@ -41103,9 +40758,6 @@
       <c r="O243" t="n">
         <v>31</v>
       </c>
-      <c r="Q243" t="n">
-        <v>0</v>
-      </c>
       <c r="R243" t="n">
         <v>0.1347164658395438</v>
       </c>
@@ -41251,9 +40903,6 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -41399,9 +41048,6 @@
       <c r="O245" t="n">
         <v>7</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -41547,9 +41193,6 @@
       <c r="O246" t="n">
         <v>222</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.964743723108991</v>
       </c>
@@ -41695,9 +41338,6 @@
       <c r="O247" t="n">
         <v>4</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -41843,9 +41483,6 @@
       <c r="O248" t="n">
         <v>169</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.7344220234478355</v>
       </c>
@@ -42092,7 +41729,7 @@
       </c>
       <c r="AM249" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN249" t="b">
@@ -42239,9 +41876,6 @@
       <c r="O250" t="n">
         <v>47</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.2042475449825341</v>
       </c>
@@ -42488,7 +42122,7 @@
       </c>
       <c r="AM251" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN251" t="b">
@@ -42630,16 +42264,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O252" t="n">
-        <v>22</v>
-      </c>
-      <c r="Q252" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="R252" t="n">
-        <v>0.09560523382161172</v>
+        <v>0.1129880036073593</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -42792,10 +42423,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="O253" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -42884,7 +42515,7 @@
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -43031,9 +42662,6 @@
       <c r="O254" t="n">
         <v>7</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.03041984712505827</v>
       </c>
@@ -43280,7 +42908,7 @@
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -43422,16 +43050,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O256" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q256" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R256" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.04345692446436896</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -43570,16 +43195,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="O257" t="n">
-        <v>170</v>
-      </c>
-      <c r="Q257" t="n">
-        <v>0</v>
+        <v>186</v>
       </c>
       <c r="R257" t="n">
-        <v>0.7387677158942723</v>
+        <v>0.8082987950372627</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43718,16 +43340,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>292</v>
+        <v>324</v>
       </c>
       <c r="O258" t="n">
-        <v>292</v>
-      </c>
-      <c r="Q258" t="n">
-        <v>0</v>
+        <v>324</v>
       </c>
       <c r="R258" t="n">
-        <v>1.268942194359574</v>
+        <v>1.408004352645554</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -43871,9 +43490,6 @@
       <c r="O259" t="n">
         <v>1</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -44014,16 +43630,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O260" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q260" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R260" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -44162,16 +43775,13 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O261" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q261" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R261" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -44324,10 +43934,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -44416,7 +44026,7 @@
       </c>
       <c r="AM262" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN262" t="b">
@@ -44558,16 +44168,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O263" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q263" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R263" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -44720,10 +44327,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O264" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
@@ -44812,7 +44419,7 @@
       </c>
       <c r="AM264" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN264" t="b">
@@ -44959,9 +44566,6 @@
       <c r="O265" t="n">
         <v>1</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -45102,16 +44706,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O266" t="n">
-        <v>13</v>
-      </c>
-      <c r="Q266" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R266" t="n">
-        <v>0.05649400180367965</v>
+        <v>0.06083969425011655</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -45255,9 +44856,6 @@
       <c r="O267" t="n">
         <v>1</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -45398,16 +44996,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O268" t="n">
-        <v>21</v>
-      </c>
-      <c r="Q268" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="R268" t="n">
-        <v>0.09125954137517482</v>
+        <v>0.1216793885002331</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -45560,10 +45155,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="O269" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -45652,7 +45247,7 @@
       </c>
       <c r="AM269" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN269" t="b">
@@ -45794,16 +45389,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O270" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q270" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R270" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.02607415467862137</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -45947,9 +45539,6 @@
       <c r="O271" t="n">
         <v>1</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -46090,16 +45679,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="O272" t="n">
-        <v>83</v>
-      </c>
-      <c r="Q272" t="n">
-        <v>0</v>
+        <v>101</v>
       </c>
       <c r="R272" t="n">
-        <v>0.3606924730542624</v>
+        <v>0.4389149370901265</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -46238,16 +45824,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O273" t="n">
-        <v>104</v>
-      </c>
-      <c r="Q273" t="n">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="R273" t="n">
-        <v>0.4519520144294372</v>
+        <v>0.5171374011259906</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -46400,10 +45983,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="O274" t="n">
-        <v>104</v>
+        <v>119</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
@@ -46492,7 +46075,7 @@
       </c>
       <c r="AM274" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN274" t="b">
@@ -46634,16 +46217,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O275" t="n">
-        <v>14</v>
-      </c>
-      <c r="Q275" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R275" t="n">
-        <v>0.06083969425011655</v>
+        <v>0.06518538669655344</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -46796,10 +46376,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O276" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
@@ -46888,7 +46468,7 @@
       </c>
       <c r="AM276" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN276" t="b">
@@ -47141,7 +46721,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8128</v>
+        <v>8230</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -39635,13 +39635,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="O236" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="R236" t="n">
-        <v>0.06953107914299034</v>
+        <v>0.08256815648230102</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -42264,13 +42264,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O252" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="R252" t="n">
-        <v>0.1129880036073593</v>
+        <v>0.12602508094667</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -42423,10 +42423,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O253" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -42657,13 +42657,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O254" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R254" t="n">
-        <v>0.03041984712505827</v>
+        <v>0.03476553957149517</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O255" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -43050,13 +43050,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O256" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R256" t="n">
-        <v>0.04345692446436896</v>
+        <v>0.04780261691080586</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -43195,13 +43195,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="O257" t="n">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="R257" t="n">
-        <v>0.8082987950372627</v>
+        <v>0.8865212590731267</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43340,13 +43340,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="O258" t="n">
-        <v>324</v>
+        <v>378</v>
       </c>
       <c r="R258" t="n">
-        <v>1.408004352645554</v>
+        <v>1.642671744753147</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -43775,13 +43775,13 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O261" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R261" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
@@ -43934,10 +43934,10 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O262" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="U262" t="inlineStr">
         <is>
@@ -44168,13 +44168,13 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O263" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R263" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S263" t="inlineStr">
         <is>
@@ -44327,10 +44327,10 @@
         </is>
       </c>
       <c r="N264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U264" t="inlineStr">
         <is>
@@ -44706,13 +44706,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O266" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R266" t="n">
-        <v>0.06083969425011655</v>
+        <v>0.06518538669655344</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -44996,13 +44996,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O268" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="R268" t="n">
-        <v>0.1216793885002331</v>
+        <v>0.1347164658395438</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -45155,10 +45155,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="O269" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -45389,13 +45389,13 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O270" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R270" t="n">
-        <v>0.02607415467862137</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -45679,13 +45679,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="O272" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="R272" t="n">
-        <v>0.4389149370901265</v>
+        <v>0.460643399322311</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -45824,13 +45824,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="O273" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="R273" t="n">
-        <v>0.5171374011259906</v>
+        <v>0.5910141727154179</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -45983,10 +45983,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="O274" t="n">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
@@ -46217,13 +46217,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O275" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R275" t="n">
-        <v>0.06518538669655344</v>
+        <v>0.06953107914299034</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -46376,10 +46376,10 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O276" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8230</v>
+        <v>8343</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -42264,13 +42264,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O252" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R252" t="n">
-        <v>0.12602508094667</v>
+        <v>0.1303707733931069</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -42423,10 +42423,10 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O253" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
@@ -42657,13 +42657,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O254" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R254" t="n">
-        <v>0.03476553957149517</v>
+        <v>0.03911123201793206</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O255" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -43195,13 +43195,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O257" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="R257" t="n">
-        <v>0.8865212590731267</v>
+        <v>0.8908669515195637</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43340,13 +43340,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="O258" t="n">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="R258" t="n">
-        <v>1.642671744753147</v>
+        <v>1.660054514538895</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -44996,13 +44996,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O268" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="R268" t="n">
-        <v>0.1347164658395438</v>
+        <v>0.1390621582859807</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -45155,10 +45155,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O269" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -45679,13 +45679,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="O272" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="R272" t="n">
-        <v>0.460643399322311</v>
+        <v>0.4693347842151848</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -45824,13 +45824,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O273" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="R273" t="n">
-        <v>0.5910141727154179</v>
+        <v>0.6214340198404762</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -45983,10 +45983,10 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="O274" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="U274" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8343</v>
+        <v>8360</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -43195,13 +43195,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="O257" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="R257" t="n">
-        <v>0.8908669515195637</v>
+        <v>0.8952126439660006</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -45795,22 +45795,22 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>D181</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Severe complicated COVID-19</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>新冠并发重症</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -45824,55 +45824,41 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="R273" t="n">
-        <v>0.6214340198404762</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U273" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="AA273" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ273" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR273" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr"/>
       <c r="AT273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
@@ -45939,7 +45925,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -45988,98 +45974,23 @@
       <c r="O274" t="n">
         <v>143</v>
       </c>
+      <c r="R274" t="n">
+        <v>0.6214340198404762</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U274" t="inlineStr">
         <is>
           <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
-      <c r="V274" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="W274" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X274" t="inlineStr">
-        <is>
-          <t>新冠併發重症</t>
-        </is>
-      </c>
-      <c r="Y274" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z274" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA274" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB274" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC274" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD274" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE274" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF274" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG274" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH274" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI274" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ274" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK274" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
-        </is>
-      </c>
-      <c r="AM274" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN274" t="b">
-        <v>1</v>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
@@ -46173,7 +46084,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -46188,17 +46099,17 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>D210</t>
+          <t>D181</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Acute hepatitis C</t>
+          <t>Severe complicated COVID-19</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>急性丙型肝炎</t>
+          <t>新冠并发重症</t>
         </is>
       </c>
       <c r="K275" t="inlineStr">
@@ -46217,22 +46128,39 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="O275" t="n">
-        <v>16</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0.06953107914299034</v>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>143</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -46240,6 +46168,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
+        <v>1</v>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46257,7 +46243,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -46332,7 +46318,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -46381,98 +46367,23 @@
       <c r="O276" t="n">
         <v>16</v>
       </c>
+      <c r="R276" t="n">
+        <v>0.06953107914299034</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U276" t="inlineStr">
         <is>
           <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
         </is>
       </c>
-      <c r="V276" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
-        </is>
-      </c>
-      <c r="W276" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X276" t="inlineStr">
-        <is>
-          <t>急性病毒性Ｃ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y276" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z276" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA276" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB276" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC276" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD276" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE276" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF276" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG276" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH276" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI276" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ276" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK276" t="inlineStr">
-        <is>
-          <t>Acute hepatitis C, code 0705.</t>
-        </is>
-      </c>
-      <c r="AM276" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN276" t="b">
-        <v>1</v>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
@@ -46538,6 +46449,240 @@
         </is>
       </c>
       <c r="BC276" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N277" t="n">
+        <v>16</v>
+      </c>
+      <c r="O277" t="n">
+        <v>16</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｃ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C, code 0705.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO277" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP277" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AT277" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU277" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV277" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ277" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA277" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB277" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC277" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -46659,7 +46804,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10">
@@ -46669,7 +46814,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11">
@@ -46721,7 +46866,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8360</v>
+        <v>8362</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -37834,13 +37834,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O225" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R225" t="n">
-        <v>0.008691384892873792</v>
+        <v>0.01303707733931069</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -39635,13 +39635,13 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="O236" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="R236" t="n">
-        <v>0.08256815648230102</v>
+        <v>0.08691384892873792</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -39780,13 +39780,13 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="O237" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="R237" t="n">
-        <v>0.25205016189334</v>
+        <v>0.2563958543397769</v>
       </c>
       <c r="S237" t="inlineStr">
         <is>
@@ -40753,13 +40753,13 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O243" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R243" t="n">
-        <v>0.1347164658395438</v>
+        <v>0.1434078507324176</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -40898,13 +40898,13 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R244" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -42657,13 +42657,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O254" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="R254" t="n">
-        <v>0.03911123201793206</v>
+        <v>0.05649400180367965</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -42816,10 +42816,10 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O255" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
@@ -43050,13 +43050,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O256" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R256" t="n">
-        <v>0.04780261691080586</v>
+        <v>0.05214830935724275</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -43195,13 +43195,13 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="O257" t="n">
-        <v>206</v>
+        <v>257</v>
       </c>
       <c r="R257" t="n">
-        <v>0.8952126439660006</v>
+        <v>1.116842958734282</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -43340,13 +43340,13 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="O258" t="n">
-        <v>382</v>
+        <v>423</v>
       </c>
       <c r="R258" t="n">
-        <v>1.660054514538895</v>
+        <v>1.838227904842807</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -43601,22 +43601,22 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>D058</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
         <is>
-          <t>Scrub Typhus</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J260" t="inlineStr">
         <is>
-          <t>恙虫病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K260" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L260" t="inlineStr">
@@ -43630,13 +43630,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R260" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -43746,22 +43746,22 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>D068</t>
+          <t>D058</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
         <is>
-          <t>Acute hepatitis B</t>
+          <t>Scrub Typhus</t>
         </is>
       </c>
       <c r="J261" t="inlineStr">
         <is>
-          <t>急性乙型肝炎</t>
+          <t>恙虫病</t>
         </is>
       </c>
       <c r="K261" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L261" t="inlineStr">
@@ -43775,55 +43775,41 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O261" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R261" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.02172846223218448</v>
       </c>
       <c r="S261" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U261" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
-        </is>
-      </c>
-      <c r="AA261" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ261" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS261" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR261" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS261" t="inlineStr"/>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
@@ -43890,7 +43876,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -43939,98 +43925,23 @@
       <c r="O262" t="n">
         <v>4</v>
       </c>
+      <c r="R262" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U262" t="inlineStr">
         <is>
           <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
-      <c r="V262" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
-        </is>
-      </c>
-      <c r="W262" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X262" t="inlineStr">
-        <is>
-          <t>急性病毒性Ｂ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y262" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z262" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB262" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC262" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD262" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE262" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF262" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG262" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH262" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI262" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ262" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK262" t="inlineStr">
-        <is>
-          <t>Acute hepatitis B, code 0703.</t>
-        </is>
-      </c>
-      <c r="AM262" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN262" t="b">
-        <v>1</v>
       </c>
       <c r="AO262" t="inlineStr">
         <is>
@@ -44124,7 +44035,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -44139,22 +44050,22 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D068</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Acute hepatitis B</t>
         </is>
       </c>
       <c r="J263" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>急性乙型肝炎</t>
         </is>
       </c>
       <c r="K263" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L263" t="inlineStr">
@@ -44173,17 +44084,34 @@
       <c r="O263" t="n">
         <v>4</v>
       </c>
-      <c r="R263" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S263" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｂ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -44191,9 +44119,67 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI263" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ263" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK263" t="inlineStr">
+        <is>
+          <t>Acute hepatitis B, code 0703.</t>
+        </is>
+      </c>
+      <c r="AM263" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN263" t="b">
+        <v>1</v>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
@@ -44203,12 +44189,12 @@
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
+          <t>SER_TW_ACUTE_HEPATITIS_B_0703</t>
         </is>
       </c>
       <c r="AT263" t="n">
@@ -44216,7 +44202,7 @@
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
@@ -44283,7 +44269,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -44332,98 +44318,23 @@
       <c r="O264" t="n">
         <v>4</v>
       </c>
+      <c r="R264" t="n">
+        <v>0.01738276978574758</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U264" t="inlineStr">
         <is>
           <t>SER_TW_SHIGELLOSIS_004</t>
         </is>
       </c>
-      <c r="V264" t="inlineStr">
-        <is>
-          <t>SER_TW_SHIGELLOSIS_004</t>
-        </is>
-      </c>
-      <c r="W264" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X264" t="inlineStr">
-        <is>
-          <t>桿菌性痢疾</t>
-        </is>
-      </c>
-      <c r="Y264" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z264" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA264" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB264" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC264" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD264" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE264" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF264" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG264" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH264" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI264" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ264" t="inlineStr">
-        <is>
-          <t>TW_NIDSS_004_current</t>
-        </is>
-      </c>
-      <c r="AK264" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
-        </is>
-      </c>
-      <c r="AM264" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN264" t="b">
-        <v>1</v>
       </c>
       <c r="AO264" t="inlineStr">
         <is>
@@ -44517,7 +44428,7 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -44532,17 +44443,17 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
@@ -44561,41 +44472,130 @@
         </is>
       </c>
       <c r="N265" t="n">
+        <v>4</v>
+      </c>
+      <c r="O265" t="n">
+        <v>4</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>桿菌性痢疾</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>TW_NIDSS_004_current</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS disease code 004, bacillary dysentery caused by Shigella; distinct from amoebiasis.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
         <v>1</v>
       </c>
-      <c r="O265" t="n">
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_TW_SHIGELLOSIS_004</t>
+        </is>
+      </c>
+      <c r="AT265" t="n">
         <v>1</v>
       </c>
-      <c r="R265" t="n">
-        <v>0.004345692446436896</v>
-      </c>
-      <c r="S265" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR265" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr"/>
-      <c r="AT265" t="n">
-        <v>0</v>
-      </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
@@ -44677,17 +44677,17 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
@@ -44706,13 +44706,13 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="O266" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R266" t="n">
-        <v>0.06518538669655344</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -44822,17 +44822,17 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K267" t="inlineStr">
@@ -44851,13 +44851,13 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="O267" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="R267" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.07822246403586412</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
@@ -44967,22 +44967,22 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>D162</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>HIV infection</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>人类免疫缺乏病毒感染</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -44996,55 +44996,41 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="O268" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="R268" t="n">
-        <v>0.1390621582859807</v>
+        <v>0.008691384892873792</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR268" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
@@ -45111,7 +45097,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -45155,103 +45141,28 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="O269" t="n">
-        <v>32</v>
+        <v>37</v>
+      </c>
+      <c r="R269" t="n">
+        <v>0.1607906205181651</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U269" t="inlineStr">
         <is>
           <t>SER_TW_HIV_044</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_TW_HIV_044</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
@@ -45345,7 +45256,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -45360,22 +45271,22 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>D165</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
         <is>
-          <t>Amebiasis</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J270" t="inlineStr">
         <is>
-          <t>阿米巴病</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -45389,41 +45300,130 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="O270" t="n">
-        <v>9</v>
-      </c>
-      <c r="R270" t="n">
-        <v>0.03911123201793206</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>37</v>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>人類免疫缺乏病毒感染(含母子垂直感染及孕產婦疑似個案)</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>NIDSS disease code 044, including source-specified vertical transmission and suspected maternal cases.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_TW_HIV_044</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
@@ -45505,22 +45505,22 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>D170</t>
+          <t>D165</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Complicated varicella</t>
+          <t>Amebiasis</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>水痘并发症</t>
+          <t>阿米巴病</t>
         </is>
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -45534,13 +45534,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O271" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="R271" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.04345692446436896</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -45650,17 +45650,17 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>D172</t>
+          <t>D170</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Severe complicated influenza</t>
+          <t>Complicated varicella</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>流感并发重症</t>
+          <t>水痘并发症</t>
         </is>
       </c>
       <c r="K272" t="inlineStr">
@@ -45679,13 +45679,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>108</v>
+        <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>0.4693347842151848</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -45795,22 +45795,22 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>D178</t>
+          <t>D172</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Acute flaccid paralysis</t>
+          <t>Severe complicated influenza</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>急性无力肢体麻痹</t>
+          <t>流感并发重症</t>
         </is>
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -45824,13 +45824,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="O273" t="n">
-        <v>1</v>
+        <v>137</v>
       </c>
       <c r="R273" t="n">
-        <v>0.004345692446436896</v>
+        <v>0.5953598651618548</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -45940,22 +45940,22 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>D181</t>
+          <t>D178</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Severe complicated COVID-19</t>
+          <t>Acute flaccid paralysis</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>新冠并发重症</t>
+          <t>急性无力肢体麻痹</t>
         </is>
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -45969,55 +45969,41 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="O274" t="n">
-        <v>143</v>
+        <v>1</v>
       </c>
       <c r="R274" t="n">
-        <v>0.6214340198404762</v>
+        <v>0.004345692446436896</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U274" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="AA274" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ274" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR274" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr"/>
       <c r="AT274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
@@ -46084,7 +46070,7 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -46128,103 +46114,28 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="O275" t="n">
-        <v>143</v>
+        <v>170</v>
+      </c>
+      <c r="R275" t="n">
+        <v>0.7387677158942723</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U275" t="inlineStr">
         <is>
           <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
-      <c r="V275" t="inlineStr">
-        <is>
-          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
-        </is>
-      </c>
-      <c r="W275" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X275" t="inlineStr">
-        <is>
-          <t>新冠併發重症</t>
-        </is>
-      </c>
-      <c r="Y275" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z275" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA275" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB275" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC275" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD275" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE275" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF275" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG275" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH275" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI275" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ275" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK275" t="inlineStr">
-        <is>
-          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
-        </is>
-      </c>
-      <c r="AM275" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN275" t="b">
-        <v>1</v>
       </c>
       <c r="AO275" t="inlineStr">
         <is>
@@ -46318,7 +46229,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -46333,17 +46244,17 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>D210</t>
+          <t>D181</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Acute hepatitis C</t>
+          <t>Severe complicated COVID-19</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>急性丙型肝炎</t>
+          <t>新冠并发重症</t>
         </is>
       </c>
       <c r="K276" t="inlineStr">
@@ -46362,22 +46273,39 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>16</v>
+        <v>170</v>
       </c>
       <c r="O276" t="n">
-        <v>16</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0.06953107914299034</v>
-      </c>
-      <c r="S276" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>170</v>
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X276" t="inlineStr">
+        <is>
+          <t>新冠併發重症</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -46385,6 +46313,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB276" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC276" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD276" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE276" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF276" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG276" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH276" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI276" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ276" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK276" t="inlineStr">
+        <is>
+          <t>Taiwan NIDSS severe complicated COVID-19 series; a severe outcome category distinct from general COVID-19 notifications.</t>
+        </is>
+      </c>
+      <c r="AM276" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN276" t="b">
+        <v>1</v>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -46402,7 +46388,7 @@
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+          <t>SER_TW_SEVERE_COMPLICATED_COVID19_19SC</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -46477,7 +46463,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -46526,98 +46512,23 @@
       <c r="O277" t="n">
         <v>16</v>
       </c>
+      <c r="R277" t="n">
+        <v>0.06953107914299034</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U277" t="inlineStr">
         <is>
           <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
         </is>
       </c>
-      <c r="V277" t="inlineStr">
-        <is>
-          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
-        </is>
-      </c>
-      <c r="W277" t="inlineStr">
-        <is>
-          <t>SRC_TW_NIDSS</t>
-        </is>
-      </c>
-      <c r="X277" t="inlineStr">
-        <is>
-          <t>急性病毒性Ｃ型肝炎</t>
-        </is>
-      </c>
-      <c r="Y277" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z277" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
       <c r="AA277" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB277" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC277" t="inlineStr">
-        <is>
-          <t>country:TW:national</t>
-        </is>
-      </c>
-      <c r="AD277" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE277" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF277" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG277" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH277" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI277" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ277" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK277" t="inlineStr">
-        <is>
-          <t>Acute hepatitis C, code 0705.</t>
-        </is>
-      </c>
-      <c r="AM277" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN277" t="b">
-        <v>1</v>
       </c>
       <c r="AO277" t="inlineStr">
         <is>
@@ -46683,6 +46594,240 @@
         </is>
       </c>
       <c r="BC277" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>tw</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Taiwan, China</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D210</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>急性丙型肝炎</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>16</v>
+      </c>
+      <c r="O278" t="n">
+        <v>16</v>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>SRC_TW_NIDSS</t>
+        </is>
+      </c>
+      <c r="X278" t="inlineStr">
+        <is>
+          <t>急性病毒性Ｃ型肝炎</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB278" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC278" t="inlineStr">
+        <is>
+          <t>country:TW:national</t>
+        </is>
+      </c>
+      <c r="AD278" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE278" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF278" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG278" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH278" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI278" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ278" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK278" t="inlineStr">
+        <is>
+          <t>Acute hepatitis C, code 0705.</t>
+        </is>
+      </c>
+      <c r="AM278" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN278" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_TW_ACUTE_HEPATITIS_C_0705</t>
+        </is>
+      </c>
+      <c r="AT278" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>open_data_csv</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>nidss_open_data</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>Taiwan, China CDC NIDSS</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
         <is>
           <t>open_data_csv</t>
         </is>
@@ -46804,7 +46949,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10">
@@ -46814,7 +46959,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11">
@@ -46866,7 +47011,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8362</v>
+        <v>8534</v>
       </c>
     </row>
     <row r="16">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29547,7 +29547,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -32859,7 +32859,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36171,7 +36171,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -38945,7 +38945,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41719,7 +41719,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42112,7 +42112,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45382,7 +45382,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29547,7 +29547,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -32859,7 +32859,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36171,7 +36171,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -38945,7 +38945,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41719,7 +41719,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42112,7 +42112,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45382,7 +45382,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29547,7 +29547,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -32859,7 +32859,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36171,7 +36171,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -38945,7 +38945,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41719,7 +41719,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42112,7 +42112,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45382,7 +45382,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">

--- a/countries/tw/2026-2029.xlsx
+++ b/countries/tw/2026-2029.xlsx
@@ -1001,7 +1001,7 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2977,7 +2977,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3373,7 +3373,7 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
@@ -5952,7 +5952,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8569,7 +8569,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -11444,7 +11444,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -14505,7 +14505,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -14901,7 +14901,7 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -17924,7 +17924,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -18320,7 +18320,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -18713,7 +18713,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -19106,7 +19106,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -20659,7 +20659,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -21052,7 +21052,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -23447,7 +23447,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -23840,7 +23840,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -24233,7 +24233,7 @@
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
@@ -24626,7 +24626,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -26179,7 +26179,7 @@
       </c>
       <c r="AJ154" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK154" t="inlineStr">
@@ -26572,7 +26572,7 @@
       </c>
       <c r="AJ156" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK156" t="inlineStr">
@@ -28284,7 +28284,7 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
@@ -29547,7 +29547,7 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
@@ -29940,7 +29940,7 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
@@ -30623,7 +30623,7 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
@@ -31016,7 +31016,7 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
@@ -32859,7 +32859,7 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
@@ -34515,7 +34515,7 @@
       </c>
       <c r="AJ205" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK205" t="inlineStr">
@@ -35778,7 +35778,7 @@
       </c>
       <c r="AJ213" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK213" t="inlineStr">
@@ -36171,7 +36171,7 @@
       </c>
       <c r="AJ215" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK215" t="inlineStr">
@@ -36564,7 +36564,7 @@
       </c>
       <c r="AJ217" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK217" t="inlineStr">
@@ -36957,7 +36957,7 @@
       </c>
       <c r="AJ219" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK219" t="inlineStr">
@@ -38945,7 +38945,7 @@
       </c>
       <c r="AJ232" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK232" t="inlineStr">
@@ -40601,7 +40601,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -41719,7 +41719,7 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
@@ -42112,7 +42112,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -42505,7 +42505,7 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
@@ -42898,7 +42898,7 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
@@ -44161,7 +44161,7 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
@@ -45382,7 +45382,7 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
@@ -46355,7 +46355,7 @@
       </c>
       <c r="AJ276" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK276" t="inlineStr">
@@ -46748,7 +46748,7 @@
       </c>
       <c r="AJ278" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK278" t="inlineStr">
